--- a/Testing Techniques.xlsx
+++ b/Testing Techniques.xlsx
@@ -9,10 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="USER MANAGEMENT" sheetId="1" r:id="rId1"/>
+    <sheet name="USER UPDATE" sheetId="3" r:id="rId2"/>
+    <sheet name="LOGIN" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="384">
   <si>
     <t>APPLICATION</t>
   </si>
@@ -639,13 +641,550 @@
   </si>
   <si>
     <t>TERMS</t>
+  </si>
+  <si>
+    <t>TEST_CASE_TECHNIQUE</t>
+  </si>
+  <si>
+    <t>LM_UU_001</t>
+  </si>
+  <si>
+    <t>USER ID / SEARCH TEXT FIELD</t>
+  </si>
+  <si>
+    <t>VERIFY THAT SEARCH TF ACCEPTS VALID NUMERIC USER ID</t>
+  </si>
+  <si>
+    <t>LM_UU_002</t>
+  </si>
+  <si>
+    <t>VERIFY THAT SEARCH TF DOES NOT ACCEPT ALPHABETS</t>
+  </si>
+  <si>
+    <t>LM_UU_003</t>
+  </si>
+  <si>
+    <t>VERIFY THAT SEARCH TF DOES NOT ACCEPT SPECIAL CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UU_004</t>
+  </si>
+  <si>
+    <t>VERIFY THAT SEARCH TF CANNOT BE LEFT BLANK</t>
+  </si>
+  <si>
+    <t>LM_UU_005</t>
+  </si>
+  <si>
+    <t>VERIFY THAT SEARCH TF ACCEPTS EXACTLY 10 DIGIT NUMBER</t>
+  </si>
+  <si>
+    <t>LM_UU_006</t>
+  </si>
+  <si>
+    <t>VERIFY THAT SEARCH TF REJECTS 9 DIGIT NUMBER</t>
+  </si>
+  <si>
+    <t>LM_UU_007</t>
+  </si>
+  <si>
+    <t>VERIFY THAT SEARCH TF REJECTS 11 DIGIT NUMBER</t>
+  </si>
+  <si>
+    <t>LM_UU_008</t>
+  </si>
+  <si>
+    <t>VERIFY THAT USER NOT FOUND MESSAGE IS SHOWN FOR INVALID ID</t>
+  </si>
+  <si>
+    <t>LM_UU_009</t>
+  </si>
+  <si>
+    <t>VERIFY THAT VALID USER DETAILS ARE LOADED ON VALID SEARCH</t>
+  </si>
+  <si>
+    <t>LM_UU_010</t>
+  </si>
+  <si>
+    <t>VERIFY THAT FIRST NAME TF ACCEPTS ONLY ALPHABETS</t>
+  </si>
+  <si>
+    <t>LM_UU_011</t>
+  </si>
+  <si>
+    <t>VERIFY THAT FIRST NAME TF DOES NOT ACCEPT NUMBERS</t>
+  </si>
+  <si>
+    <t>LM_UU_012</t>
+  </si>
+  <si>
+    <t>VERIFY THAT FIRST NAME TF DOES NOT ACCEPT SPECIAL CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UU_013</t>
+  </si>
+  <si>
+    <t>VERIFY THAT FIRST NAME TF CANNOT BE EMPTY</t>
+  </si>
+  <si>
+    <t>LM_UU_014</t>
+  </si>
+  <si>
+    <t>VERIFY THAT FIRST NAME TF ACCEPTS 25 CHARACTERS (MAX)</t>
+  </si>
+  <si>
+    <t>LM_UU_015</t>
+  </si>
+  <si>
+    <t>VERIFY THAT FIRST NAME TF REJECTS MORE THAN 25 CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UU_016</t>
+  </si>
+  <si>
+    <t>VERIFY THAT FIRST NAME TF ACCEPTS 24 CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UU_017</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LAST NAME TF ACCEPTS ONLY ALPHABETS</t>
+  </si>
+  <si>
+    <t>LM_UU_018</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LAST NAME TF DOES NOT ACCEPT NUMBERS</t>
+  </si>
+  <si>
+    <t>LM_UU_019</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LAST NAME TF DOES NOT ACCEPT SPECIAL CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UU_020</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LAST NAME TF CANNOT BE EMPTY</t>
+  </si>
+  <si>
+    <t>LM_UU_021</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LAST NAME TF ACCEPTS 30 CHARACTERS (MAX)</t>
+  </si>
+  <si>
+    <t>LM_UU_022</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LAST NAME TF REJECTS MORE THAN 30 CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UU_023</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LAST NAME TF ACCEPTS 29 CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UU_024</t>
+  </si>
+  <si>
+    <t>EMAIL TEXT FIELD</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL TF ACCEPTS VALID EMAIL FORMAT (abc@domain.com)</t>
+  </si>
+  <si>
+    <t>LM_UU_025</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL TF REJECTS INVALID EMAIL FORMAT (NO @)</t>
+  </si>
+  <si>
+    <t>LM_UU_026</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL TF REJECTS INVALID EMAIL FORMAT (NO DOMAIN)</t>
+  </si>
+  <si>
+    <t>LM_UU_027</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL TF CANNOT BE EMPTY</t>
+  </si>
+  <si>
+    <t>LM_UU_028</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL ALREADY EXISTS MESSAGE IS SHOWN FOR DUPLICATE</t>
+  </si>
+  <si>
+    <t>LM_UU_029</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL TF ACCEPTS UNIQUE EMAIL FOR ANOTHER USER</t>
+  </si>
+  <si>
+    <t>LM_UU_030</t>
+  </si>
+  <si>
+    <t>PHONE NUMBER TEXT FIELD</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PHONE TF ACCEPTS EXACTLY 10 DIGIT NUMERIC VALUE</t>
+  </si>
+  <si>
+    <t>LM_UU_031</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PHONE TF DOES NOT ACCEPT ALPHABETS</t>
+  </si>
+  <si>
+    <t>LM_UU_032</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PHONE TF DOES NOT ACCEPT SPECIAL CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UU_033</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PHONE TF CANNOT BE EMPTY</t>
+  </si>
+  <si>
+    <t>LM_UU_034</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PHONE TF REJECTS 9 DIGIT NUMBER</t>
+  </si>
+  <si>
+    <t>LM_UU_035</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PHONE TF REJECTS 11 DIGIT NUMBER</t>
+  </si>
+  <si>
+    <t>LM_UU_036</t>
+  </si>
+  <si>
+    <t>ROLE DROPDOWN</t>
+  </si>
+  <si>
+    <t>VERIFY THAT ROLE DD SHOWS OPTIONS: ADMIN, LIBRARIAN, MEMBER</t>
+  </si>
+  <si>
+    <t>LM_UU_037</t>
+  </si>
+  <si>
+    <t>VERIFY THAT ONLY 1 OPTION CAN BE SELECTED FROM ROLE DROPDOWN</t>
+  </si>
+  <si>
+    <t>LM_UU_038</t>
+  </si>
+  <si>
+    <t>VERIFY THAT ROLE DROPDOWN CANNOT BE LEFT BLANK</t>
+  </si>
+  <si>
+    <t>LM_UU_039</t>
+  </si>
+  <si>
+    <t>STATUS RADIO BUTTONS</t>
+  </si>
+  <si>
+    <t>VERIFY THAT STATUS RB SHOWS OPTIONS: ACTIVE, INACTIVE</t>
+  </si>
+  <si>
+    <t>LM_UU_040</t>
+  </si>
+  <si>
+    <t>VERIFY THAT ONLY 1 OPTION CAN BE SELECTED FROM STATUS RADIO</t>
+  </si>
+  <si>
+    <t>LM_UU_041</t>
+  </si>
+  <si>
+    <t>VERIFY THAT STATUS RADIO CANNOT BE LEFT UNSELECTED</t>
+  </si>
+  <si>
+    <t>LM_UU_042</t>
+  </si>
+  <si>
+    <t>UPDATE BUTTON</t>
+  </si>
+  <si>
+    <t>VERIFY THAT UPDATE BUTTON IS ENABLED WHEN ALL FIELDS ARE VALID</t>
+  </si>
+  <si>
+    <t>LM_UU_043</t>
+  </si>
+  <si>
+    <t>VERIFY THAT UPDATE BUTTON VALIDATES ALL FIELDS ON CLICK</t>
+  </si>
+  <si>
+    <t>LM_UU_044</t>
+  </si>
+  <si>
+    <t>VERIFY THAT SUCCESS MESSAGE IS SHOWN ON VALID UPDATE</t>
+  </si>
+  <si>
+    <t>LM_UU_045</t>
+  </si>
+  <si>
+    <t>VERIFY THAT ERROR MESSAGES ARE SHOWN FOR INVALID FIELDS</t>
+  </si>
+  <si>
+    <t>LM_UU_046</t>
+  </si>
+  <si>
+    <t>VERIFY THAT UPDATE DOES NOT PROCEED WITH EMPTY MANDATORY FIELDS</t>
+  </si>
+  <si>
+    <t>LM_UU_047</t>
+  </si>
+  <si>
+    <t>VERIFY THAT DUPLICATE EMAIL ERROR IS SHOWN ON UPDATE</t>
+  </si>
+  <si>
+    <t>LM_UU_048</t>
+  </si>
+  <si>
+    <t>VERIFY THAT NO CHANGES DETECTED MESSAGE IS SHOWN IF NO FIELD MODIFIED</t>
+  </si>
+  <si>
+    <t>LM_UU_049</t>
+  </si>
+  <si>
+    <t>VERIFY THAT UPDATE ACTION IS NOT PERFORMED WHEN NO CHANGES ARE MADE</t>
+  </si>
+  <si>
+    <t>LM_UU_050</t>
+  </si>
+  <si>
+    <t>VERIFY THAT CANCEL BUTTON CLEARS ALL UNSAVED CHANGES IN FIELDS</t>
+  </si>
+  <si>
+    <t>LM_UU_051</t>
+  </si>
+  <si>
+    <t>VERIFY THAT CANCEL BUTTON NAVIGATES BACK TO USER LIST / DASHBOARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APPLICATION </t>
+  </si>
+  <si>
+    <t>USER UPDATE</t>
+  </si>
+  <si>
+    <t>LM_UL_001</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL TF ACCEPTS VALID REGISTERED EMAIL FORMAT</t>
+  </si>
+  <si>
+    <t>LM_UL_002</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL TF REJECTS INVALID EMAIL FORMAT (MISSING @)</t>
+  </si>
+  <si>
+    <t>LM_UL_003</t>
+  </si>
+  <si>
+    <t>LM_UL_004</t>
+  </si>
+  <si>
+    <t>LM_UL_005</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL TF ACCEPTS MAX 50 CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UL_006</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL TF REJECTS MORE THAN 50 CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UL_007</t>
+  </si>
+  <si>
+    <t>VERIFY THAT INVALID EMAIL MESSAGE IS SHOWN FOR WRONG FORMAT</t>
+  </si>
+  <si>
+    <t>LM_UL_008</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL NOT REGISTERED MESSAGE IS SHOWN FOR UNKNOWN EMAIL</t>
+  </si>
+  <si>
+    <t>LM_UL_009</t>
+  </si>
+  <si>
+    <t>PASSWORD TEXT FIELD</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD TF ACCEPTS VALID PASSWORD (8-20 CHARS)</t>
+  </si>
+  <si>
+    <t>LM_UL_010</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD TF CANNOT BE EMPTY</t>
+  </si>
+  <si>
+    <t>LM_UL_011</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD TF ACCEPTS MINIMUM 8 CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UL_012</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD TF REJECTS LESS THAN 8 CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UL_013</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD TF ACCEPTS MAX 20 CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UL_014</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD TF REJECTS MORE THAN 20 CHARACTERS</t>
+  </si>
+  <si>
+    <t>LM_UL_015</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD MUST CONTAIN AT LEAST 1 UPPERCASE LETTER</t>
+  </si>
+  <si>
+    <t>LM_UL_016</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD MUST CONTAIN AT LEAST 1 LOWERCASE LETTER</t>
+  </si>
+  <si>
+    <t>LM_UL_017</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD MUST CONTAIN AT LEAST 1 NUMBER</t>
+  </si>
+  <si>
+    <t>LM_UL_018</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD MUST CONTAIN AT LEAST 1 SPECIAL CHARACTER</t>
+  </si>
+  <si>
+    <t>LM_UL_019</t>
+  </si>
+  <si>
+    <t>VERIFY THAT PASSWORD CHARACTERS ARE MASKED (SHOWN AS ****)</t>
+  </si>
+  <si>
+    <t>LM_UL_020</t>
+  </si>
+  <si>
+    <t>VERIFY THAT INVALID PASSWORD FORMAT MESSAGE IS SHOWN FOR INVALID PW</t>
+  </si>
+  <si>
+    <t>LM_UL_021</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LOGIN BUTTON IS ENABLED WHEN BOTH FIELDS ARE FILLED</t>
+  </si>
+  <si>
+    <t>LM_UL_022</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LOGIN BUTTON IS DISABLED WHEN EMAIL FIELD IS EMPTY</t>
+  </si>
+  <si>
+    <t>LM_UL_023</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LOGIN BUTTON IS DISABLED WHEN PASSWORD FIELD IS EMPTY</t>
+  </si>
+  <si>
+    <t>LM_UL_024</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LOGIN VALIDATES EMAIL AND PASSWORD ON CLICK</t>
+  </si>
+  <si>
+    <t>LM_UL_025</t>
+  </si>
+  <si>
+    <t>VERIFY THAT VALID CREDENTIALS REDIRECT TO MEMBER DASHBOARD</t>
+  </si>
+  <si>
+    <t>LM_UL_026</t>
+  </si>
+  <si>
+    <t>VERIFY THAT INVALID CREDENTIALS SHOW APPROPRIATE ERROR MESSAGE</t>
+  </si>
+  <si>
+    <t>LM_UL_027</t>
+  </si>
+  <si>
+    <t>VERIFY THAT ACCOUNT ALLOWS MAX 3 CONSECUTIVE FAILED ATTEMPTS</t>
+  </si>
+  <si>
+    <t>LM_UL_028</t>
+  </si>
+  <si>
+    <t>VERIFY THAT ACCOUNT IS LOCKED AFTER 3 CONSECUTIVE FAILED ATTEMPTS</t>
+  </si>
+  <si>
+    <t>LM_UL_029</t>
+  </si>
+  <si>
+    <t>VERIFY THAT ACCOUNT LOCK MESSAGE IS DISPLAYED AFTER 3 FAILURES</t>
+  </si>
+  <si>
+    <t>LM_UL_030</t>
+  </si>
+  <si>
+    <t>VERIFY THAT LOCKED ACCOUNT REMAINS LOCKED FOR 15 MINUTES</t>
+  </si>
+  <si>
+    <t>LM_UL_031</t>
+  </si>
+  <si>
+    <t>VERIFY THAT ACCOUNT IS UNLOCKED AFTER 15 MINUTE LOCK PERIOD</t>
+  </si>
+  <si>
+    <t>LM_UL_032</t>
+  </si>
+  <si>
+    <t>VERIFY THAT FAILED ATTEMPT COUNTER RESETS ON SUCCESSFUL LOGIN</t>
+  </si>
+  <si>
+    <t>LM_UL_033</t>
+  </si>
+  <si>
+    <t>VERIFY THAT 2 FAILED ATTEMPTS DO NOT LOCK THE ACCOUNT</t>
+  </si>
+  <si>
+    <t>USER LOGIN</t>
+  </si>
+  <si>
+    <t>ACCOUNT LOCK</t>
+  </si>
+  <si>
+    <t>LOGIN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -661,6 +1200,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -670,7 +1233,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -678,19 +1241,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2655,4 +3260,1428 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B57" s="10"/>
+      <c r="C57" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="3"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B7:B15"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B30:B35"/>
+    <mergeCell ref="B16:B22"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B23:B29"/>
+    <mergeCell ref="B48:B56"/>
+    <mergeCell ref="B45:B47"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B21" s="8"/>
+      <c r="C21" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B23" s="8"/>
+      <c r="C23" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B31:B39"/>
+    <mergeCell ref="B7:B14"/>
+    <mergeCell ref="B15:B26"/>
+    <mergeCell ref="B27:B30"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Testing Techniques.xlsx
+++ b/Testing Techniques.xlsx
@@ -4542,9 +4542,7 @@
       <c r="A31" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>382</v>
-      </c>
+      <c r="B31" s="11"/>
       <c r="C31" s="7" t="s">
         <v>364</v>
       </c>
@@ -4559,7 +4557,7 @@
       <c r="A32" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="B32" s="9"/>
+      <c r="B32" s="11"/>
       <c r="C32" s="7" t="s">
         <v>366</v>
       </c>
@@ -4574,7 +4572,9 @@
       <c r="A33" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="B33" s="9"/>
+      <c r="B33" s="11" t="s">
+        <v>382</v>
+      </c>
       <c r="C33" s="7" t="s">
         <v>368</v>
       </c>
@@ -4589,7 +4589,7 @@
       <c r="A34" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B34" s="9"/>
+      <c r="B34" s="11"/>
       <c r="C34" s="7" t="s">
         <v>370</v>
       </c>
@@ -4604,7 +4604,7 @@
       <c r="A35" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="B35" s="9"/>
+      <c r="B35" s="11"/>
       <c r="C35" s="7" t="s">
         <v>372</v>
       </c>
@@ -4619,7 +4619,7 @@
       <c r="A36" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="B36" s="9"/>
+      <c r="B36" s="11"/>
       <c r="C36" s="7" t="s">
         <v>374</v>
       </c>
@@ -4634,7 +4634,7 @@
       <c r="A37" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="B37" s="9"/>
+      <c r="B37" s="11"/>
       <c r="C37" s="7" t="s">
         <v>376</v>
       </c>
@@ -4649,7 +4649,7 @@
       <c r="A38" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B38" s="9"/>
+      <c r="B38" s="11"/>
       <c r="C38" s="7" t="s">
         <v>378</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="A39" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B39" s="9"/>
+      <c r="B39" s="11"/>
       <c r="C39" s="7" t="s">
         <v>380</v>
       </c>
@@ -4677,10 +4677,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B31:B39"/>
     <mergeCell ref="B7:B14"/>
     <mergeCell ref="B15:B26"/>
-    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="B33:B39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
